--- a/synthetic_data/academic_validation_report.xlsx
+++ b/synthetic_data/academic_validation_report.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,9 +147,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -561,7 +558,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>9,890 sinh viên</t>
+          <t>1,500 sinh viên</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -583,12 +580,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>5,359 / 9,890 SV (Bao gồm cả các khóa đang học)</t>
+          <t>0 / 1,500 SV (Bao gồm cả các khóa đang học)</t>
         </is>
       </c>
     </row>
@@ -605,12 +602,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>4,445 / 4,898 SV hoàn tất lộ trình đào tạo chuẩn</t>
+          <t>0 / 1,500 SV hoàn tất lộ trình đào tạo chuẩn</t>
         </is>
       </c>
     </row>
@@ -627,12 +624,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>10 SV đạt chuẩn học vượt toàn khóa</t>
+          <t>0 SV đạt chuẩn học vượt toàn khóa</t>
         </is>
       </c>
     </row>
@@ -649,12 +646,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2,598 SV (Chiếm tỷ lệ đa số theo tiến độ chuẩn)</t>
+          <t>0 SV (Chiếm tỷ lệ đa số theo tiến độ chuẩn)</t>
         </is>
       </c>
     </row>
@@ -671,12 +668,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>2,751 SV (Trả nợ môn, tích lũy thêm CTXH/tiếng Anh)</t>
+          <t>0 SV (Trả nợ môn, tích lũy thêm CTXH/tiếng Anh)</t>
         </is>
       </c>
     </row>
@@ -693,12 +690,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>323 SV tốt nghiệp</t>
+          <t>0 SV tốt nghiệp</t>
         </is>
       </c>
     </row>
@@ -715,12 +712,12 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>1,808 SV tốt nghiệp</t>
+          <t>0 SV tốt nghiệp</t>
         </is>
       </c>
     </row>
@@ -737,7 +734,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -759,7 +756,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -781,12 +778,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>518 SV tốt nghiệp</t>
+          <t>0 SV tốt nghiệp</t>
         </is>
       </c>
     </row>
@@ -803,7 +800,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>2.75 / 4.0</t>
+          <t>2.61 / 4.0</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -825,12 +822,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>7.05 / 10.0</t>
+          <t>8.31 / 10.0</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Tổng cộng 345,992 lượt điểm học phần</t>
+          <t>Tổng cộng 9,315 lượt điểm học phần</t>
         </is>
       </c>
     </row>
@@ -847,7 +844,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>1.23 điểm</t>
+          <t>2.56 điểm</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -869,12 +866,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>9,113 / 9,890 sinh viên</t>
+          <t>1,106 / 1,500 sinh viên</t>
         </is>
       </c>
     </row>
@@ -891,7 +888,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>16.6 ngày</t>
+          <t>1.9 ngày</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -913,12 +910,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>513 / 9,890 sinh viên</t>
+          <t>1 / 1,500 sinh viên</t>
         </is>
       </c>
     </row>
@@ -935,12 +932,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>100 sinh viên</t>
+          <t>1 sinh viên</t>
         </is>
       </c>
     </row>
@@ -957,12 +954,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>413 sinh viên vi phạm khung thời gian</t>
+          <t>0 sinh viên vi phạm khung thời gian</t>
         </is>
       </c>
     </row>
@@ -979,12 +976,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>44 sinh viên từng bị tạm dừng kỳ học</t>
+          <t>0 sinh viên từng bị tạm dừng kỳ học</t>
         </is>
       </c>
     </row>
@@ -999,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1012,7 +1009,7 @@
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
@@ -1117,812 +1114,58 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>K13</t>
+          <t>K20</t>
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>502</v>
+        <v>1500</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>0.9203187250996016</v>
+        <v>0</v>
       </c>
       <c r="E2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>1499</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>0.9993333333333333</v>
+      </c>
+      <c r="J2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="9" t="n">
-        <v>203</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>258</v>
-      </c>
-      <c r="H2" s="9" t="n">
+      <c r="K2" s="10" t="n">
+        <v>0.0006666666666666666</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>2.608811777850047</v>
+      </c>
+      <c r="M2" s="11" t="n">
+        <v>14.75133333333333</v>
+      </c>
+      <c r="N2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="O2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>0.0796812749003984</v>
-      </c>
-      <c r="L2" s="11" t="n">
-        <v>2.781137329455334</v>
-      </c>
-      <c r="M2" s="11" t="n">
-        <v>119.0358565737052</v>
-      </c>
-      <c r="N2" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="O2" s="9" t="n">
-        <v>160</v>
-      </c>
       <c r="P2" s="9" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R2" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>K14</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="n">
-        <v>534</v>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>467</v>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>0.8745318352059925</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>207</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>259</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13" t="n">
-        <v>67</v>
-      </c>
-      <c r="K3" s="14" t="n">
-        <v>0.1254681647940075</v>
-      </c>
-      <c r="L3" s="15" t="n">
-        <v>2.772104238995573</v>
-      </c>
-      <c r="M3" s="15" t="n">
-        <v>118.6498127340824</v>
-      </c>
-      <c r="N3" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="O3" s="13" t="n">
-        <v>157</v>
-      </c>
-      <c r="P3" s="13" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q3" s="15" t="n">
-        <v>115</v>
-      </c>
-      <c r="R3" s="15" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>K15</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>565</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>515</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>0.911504424778761</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>207</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>307</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>0.08849557522123894</v>
-      </c>
-      <c r="L4" s="11" t="n">
-        <v>2.762538687985129</v>
-      </c>
-      <c r="M4" s="11" t="n">
-        <v>118.9823008849557</v>
-      </c>
-      <c r="N4" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="O4" s="9" t="n">
-        <v>185</v>
-      </c>
-      <c r="P4" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q4" s="11" t="n">
-        <v>108</v>
-      </c>
-      <c r="R4" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>K16</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>597</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>545</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>0.9128978224455612</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>243</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>301</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <v>0.08710217755443886</v>
-      </c>
-      <c r="L5" s="15" t="n">
-        <v>2.749967820938581</v>
-      </c>
-      <c r="M5" s="15" t="n">
-        <v>119.3802345058626</v>
-      </c>
-      <c r="N5" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="O5" s="13" t="n">
-        <v>187</v>
-      </c>
-      <c r="P5" s="13" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q5" s="15" t="n">
-        <v>125</v>
-      </c>
-      <c r="R5" s="15" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>K17</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>628</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>566</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>0.9012738853503185</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>257</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>308</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>62</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>0.09872611464968153</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>2.796202320216249</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>118.8200636942675</v>
-      </c>
-      <c r="N6" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="O6" s="9" t="n">
-        <v>199</v>
-      </c>
-      <c r="P6" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q6" s="11" t="n">
-        <v>142</v>
-      </c>
-      <c r="R6" s="11" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>K18</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>659</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>594</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>0.9013657056145675</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>274</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>319</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>65</v>
-      </c>
-      <c r="K7" s="14" t="n">
-        <v>0.09863429438543247</v>
-      </c>
-      <c r="L7" s="15" t="n">
-        <v>2.701366300395138</v>
-      </c>
-      <c r="M7" s="15" t="n">
-        <v>119.6327769347496</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="O7" s="13" t="n">
-        <v>190</v>
-      </c>
-      <c r="P7" s="13" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q7" s="15" t="n">
-        <v>119</v>
-      </c>
-      <c r="R7" s="15" t="n">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>K19</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>691</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>636</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.9204052098408104</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>285</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>350</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>0.07959479015918958</v>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>2.720213235554745</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>119.7916063675832</v>
-      </c>
-      <c r="N8" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="O8" s="9" t="n">
-        <v>206</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q8" s="11" t="n">
-        <v>130</v>
-      </c>
-      <c r="R8" s="11" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>K20</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>722</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>660</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>0.9141274238227147</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>298</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>361</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>62</v>
-      </c>
-      <c r="K9" s="14" t="n">
-        <v>0.08587257617728532</v>
-      </c>
-      <c r="L9" s="15" t="n">
-        <v>2.784277773422986</v>
-      </c>
-      <c r="M9" s="15" t="n">
-        <v>119.4362880886427</v>
-      </c>
-      <c r="N9" s="13" t="n">
-        <v>47</v>
-      </c>
-      <c r="O9" s="13" t="n">
-        <v>222</v>
-      </c>
-      <c r="P9" s="13" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q9" s="15" t="n">
-        <v>138</v>
-      </c>
-      <c r="R9" s="15" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>K21</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>754</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>580</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>311</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>268</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>169</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>0.2241379310344828</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>0.006631299734748011</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>2.764923559070016</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>118.4960212201592</v>
-      </c>
-      <c r="N10" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="O10" s="9" t="n">
-        <v>197</v>
-      </c>
-      <c r="P10" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q10" s="11" t="n">
-        <v>158</v>
-      </c>
-      <c r="R10" s="11" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>K22</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>785</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>334</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>0.4254777070063694</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>313</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>437</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>0.556687898089172</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>0.0178343949044586</v>
-      </c>
-      <c r="L11" s="15" t="n">
-        <v>2.746247058651164</v>
-      </c>
-      <c r="M11" s="15" t="n">
-        <v>114.3197452229299</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>105</v>
-      </c>
-      <c r="P11" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q11" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="R11" s="15" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>K23</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>816</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>808</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>0.9901960784313726</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>0.009803921568627451</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>2.72753625894905</v>
-      </c>
-      <c r="M12" s="11" t="n">
-        <v>107.8419117647059</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>K24</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>848</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>843</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>0.9941037735849056</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" s="14" t="n">
-        <v>0.00589622641509434</v>
-      </c>
-      <c r="L13" s="15" t="n">
-        <v>2.753132915370406</v>
-      </c>
-      <c r="M13" s="15" t="n">
-        <v>72.36556603773585</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>K25</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>879</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>870</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>0.9897610921501706</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" s="10" t="n">
-        <v>0.01023890784982935</v>
-      </c>
-      <c r="L14" s="11" t="n">
-        <v>2.730665743794649</v>
-      </c>
-      <c r="M14" s="11" t="n">
-        <v>34.62798634812287</v>
-      </c>
-      <c r="N14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>K26</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>910</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>891</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>0.9791208791208791</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="K15" s="14" t="n">
-        <v>0.02087912087912088</v>
-      </c>
-      <c r="L15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1943,7 +1186,7 @@
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1986,10 +1229,10 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>2964</v>
+        <v>57</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>0.0085666720617817</v>
+        <v>0.008558558558558501</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -2009,10 +1252,10 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>12482</v>
+        <v>388</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>0.0360759786353441</v>
+        <v>0.0582582582582582</v>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
@@ -2032,10 +1275,10 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>20786</v>
+        <v>530</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.0600765335614696</v>
+        <v>0.07957957957957951</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -2055,10 +1298,10 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>67362</v>
+        <v>1428</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>0.1946923628291983</v>
+        <v>0.2144144144144144</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -2078,10 +1321,10 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>54320</v>
+        <v>1016</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.1569978496612638</v>
+        <v>0.1525525525525525</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -2101,10 +1344,10 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>97659</v>
+        <v>1872</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>0.282257971282573</v>
+        <v>0.2810810810810811</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
@@ -2124,10 +1367,10 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>49329</v>
+        <v>794</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.1425726606395523</v>
+        <v>0.1192192192192192</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -2147,10 +1390,10 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>36362</v>
+        <v>524</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>0.1050949154893754</v>
+        <v>0.0786786786786786</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -2170,10 +1413,10 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>4728</v>
+        <v>51</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.0136650558394413</v>
+        <v>0.0076576576576576</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -2216,10 +1459,10 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>2.312192189414784e-05</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -2239,10 +1482,10 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>264</v>
+        <v>6</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>0.0007630234225068</v>
+        <v>0.0009009009009009</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
@@ -2262,10 +1505,10 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>2692</v>
+        <v>51</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.0077805267173807</v>
+        <v>0.0076576576576576</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -2285,10 +1528,10 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>12482</v>
+        <v>388</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>0.0360759786353441</v>
+        <v>0.0582582582582582</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
@@ -2308,10 +1551,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>54955</v>
+        <v>1295</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.1588331522116118</v>
+        <v>0.1944444444444444</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -2331,10 +1574,10 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>87513</v>
+        <v>1679</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>0.25293359384032</v>
+        <v>0.2521021021021021</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
@@ -2354,10 +1597,10 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>97659</v>
+        <v>1872</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.282257971282573</v>
+        <v>0.2810810810810811</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -2377,10 +1620,10 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>74545</v>
+        <v>1157</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>0.2154529584499063</v>
+        <v>0.1737237237237237</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -2400,10 +1643,10 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>15874</v>
+        <v>212</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.0458796735184628</v>
+        <v>0.0318318318318318</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>

--- a/synthetic_data/academic_validation_report.xlsx
+++ b/synthetic_data/academic_validation_report.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,6 +147,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -558,7 +561,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>1,500 sinh viên</t>
+          <t>11,092 sinh viên</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -580,12 +583,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>0 / 1,500 SV (Bao gồm cả các khóa đang học)</t>
+          <t>3,758 / 11,092 SV (Bao gồm cả các khóa đang học)</t>
         </is>
       </c>
     </row>
@@ -602,12 +605,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0 / 1,500 SV hoàn tất lộ trình đào tạo chuẩn</t>
+          <t>1,394 / 1,500 SV hoàn tất lộ trình đào tạo chuẩn</t>
         </is>
       </c>
     </row>
@@ -624,12 +627,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>0 SV đạt chuẩn học vượt toàn khóa</t>
+          <t>55 SV đạt chuẩn học vượt toàn khóa</t>
         </is>
       </c>
     </row>
@@ -646,12 +649,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0 SV (Chiếm tỷ lệ đa số theo tiến độ chuẩn)</t>
+          <t>2,294 SV (Chiếm tỷ lệ đa số theo tiến độ chuẩn)</t>
         </is>
       </c>
     </row>
@@ -668,12 +671,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>0 SV (Trả nợ môn, tích lũy thêm CTXH/tiếng Anh)</t>
+          <t>1,409 SV (Trả nợ môn, tích lũy thêm CTXH/tiếng Anh)</t>
         </is>
       </c>
     </row>
@@ -690,12 +693,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0 SV tốt nghiệp</t>
+          <t>205 SV tốt nghiệp</t>
         </is>
       </c>
     </row>
@@ -712,12 +715,12 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>0 SV tốt nghiệp</t>
+          <t>785 SV tốt nghiệp</t>
         </is>
       </c>
     </row>
@@ -734,7 +737,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -756,7 +759,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -778,12 +781,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0 SV tốt nghiệp</t>
+          <t>767 SV tốt nghiệp</t>
         </is>
       </c>
     </row>
@@ -800,7 +803,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>2.61 / 4.0</t>
+          <t>2.60 / 4.0</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -822,12 +825,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>8.31 / 10.0</t>
+          <t>7.15 / 10.0</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Tổng cộng 9,315 lượt điểm học phần</t>
+          <t>Tổng cộng 290,979 lượt điểm học phần</t>
         </is>
       </c>
     </row>
@@ -844,7 +847,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2.56 điểm</t>
+          <t>1.78 điểm</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -866,12 +869,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1,106 / 1,500 sinh viên</t>
+          <t>10,210 / 11,092 sinh viên</t>
         </is>
       </c>
     </row>
@@ -888,7 +891,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>1.9 ngày</t>
+          <t>12.6 ngày</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -910,12 +913,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>1 / 1,500 sinh viên</t>
+          <t>215 / 11,092 sinh viên</t>
         </is>
       </c>
     </row>
@@ -932,12 +935,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>1 sinh viên</t>
+          <t>123 sinh viên</t>
         </is>
       </c>
     </row>
@@ -954,12 +957,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>0 sinh viên vi phạm khung thời gian</t>
+          <t>92 sinh viên vi phạm khung thời gian</t>
         </is>
       </c>
     </row>
@@ -976,12 +979,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>0 sinh viên từng bị tạm dừng kỳ học</t>
+          <t>93 sinh viên từng bị tạm dừng kỳ học</t>
         </is>
       </c>
     </row>
@@ -996,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1009,7 +1012,7 @@
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
@@ -1121,51 +1124,399 @@
         <v>1500</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>0</v>
+        <v>1394</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>0</v>
+        <v>0.9293333333333333</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>1499</v>
+        <v>0</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>0.9993333333333333</v>
+        <v>0</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="K2" s="10" t="n">
-        <v>0.0006666666666666666</v>
+        <v>0.07066666666666667</v>
       </c>
       <c r="L2" s="11" t="n">
-        <v>2.608811777850047</v>
+        <v>2.603131700014104</v>
       </c>
       <c r="M2" s="11" t="n">
-        <v>14.75133333333333</v>
+        <v>101.8</v>
       </c>
       <c r="N2" s="9" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="O2" s="9" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="Q2" s="11" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="R2" s="11" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>K21</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>1520</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>1342</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>0.8828947368421053</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>769</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>555</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>157</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>0.1032894736842105</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>0.01381578947368421</v>
+      </c>
+      <c r="L3" s="15" t="n">
+        <v>2.613476616275755</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>107.1967105263158</v>
+      </c>
+      <c r="N3" s="13" t="n">
+        <v>67</v>
+      </c>
+      <c r="O3" s="13" t="n">
+        <v>270</v>
+      </c>
+      <c r="P3" s="13" t="n">
+        <v>326</v>
+      </c>
+      <c r="Q3" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>K22</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>1559</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>0.6555484284797948</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>763</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>240</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>522</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0.3348300192431046</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>0.009621552277100705</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>2.610016050148459</v>
+      </c>
+      <c r="M4" s="11" t="n">
+        <v>105.6061577934573</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>231</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q4" s="11" t="n">
+        <v>121</v>
+      </c>
+      <c r="R4" s="11" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>K23</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>1577</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>1557</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.9873176918199112</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.01268230818008878</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>2.586226455156785</v>
+      </c>
+      <c r="M5" s="15" t="n">
+        <v>92.3855421686747</v>
+      </c>
+      <c r="N5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>K24</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>1621</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0.987045033929673</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>0.01295496607032696</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>2.597070188789299</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>60.34053053670574</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>K25</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>1648</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>1634</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.991504854368932</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>0.008495145631067961</v>
+      </c>
+      <c r="L7" s="15" t="n">
+        <v>2.572179346154756</v>
+      </c>
+      <c r="M7" s="15" t="n">
+        <v>30.4368932038835</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>K26</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>1667</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>1649</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>0.9892021595680864</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>0.01079784043191362</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1186,7 +1537,7 @@
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1229,10 +1580,10 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>57</v>
+        <v>4439</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>0.008558558558558501</v>
+        <v>0.016328497439821</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -1252,10 +1603,10 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>388</v>
+        <v>15651</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>0.0582582582582582</v>
+        <v>0.0575709198987699</v>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
@@ -1275,10 +1626,10 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>530</v>
+        <v>22332</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.07957957957957951</v>
+        <v>0.0821464304631864</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -1298,10 +1649,10 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1428</v>
+        <v>56923</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>0.2144144144144144</v>
+        <v>0.2093865870166558</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -1321,10 +1672,10 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>1016</v>
+        <v>39690</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.1525525525525525</v>
+        <v>0.1459964098640456</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -1344,10 +1695,10 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1872</v>
+        <v>78796</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>0.2810810810810811</v>
+        <v>0.2898446236242716</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
@@ -1367,10 +1718,10 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>794</v>
+        <v>31862</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.1192192192192192</v>
+        <v>0.1172017538696957</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -1390,10 +1741,10 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>524</v>
+        <v>19970</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>0.0786786786786786</v>
+        <v>0.0734580071802719</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -1413,10 +1764,10 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>51</v>
+        <v>2193</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.0076576576576576</v>
+        <v>0.0080667706432817</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -1459,10 +1810,10 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0</v>
+        <v>1.839208992996292e-05</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -1482,10 +1833,10 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>6</v>
+        <v>425</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>0.0009009009009009</v>
+        <v>0.0015633276440468</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
@@ -1505,10 +1856,10 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>51</v>
+        <v>4009</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.0076576576576576</v>
+        <v>0.0147467777058442</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -1528,10 +1879,10 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>388</v>
+        <v>15651</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>0.0582582582582582</v>
+        <v>0.0575709198987699</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
@@ -1551,10 +1902,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1295</v>
+        <v>51661</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.1944444444444444</v>
+        <v>0.1900307515743629</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1574,10 +1925,10 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1679</v>
+        <v>67284</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>0.2521021021021021</v>
+        <v>0.247498675769525</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
@@ -1597,10 +1948,10 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1872</v>
+        <v>78796</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.2810810810810811</v>
+        <v>0.2898446236242716</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1620,10 +1971,10 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1157</v>
+        <v>45651</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>0.1737237237237237</v>
+        <v>0.1679234594785474</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1643,10 +1994,10 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>212</v>
+        <v>8374</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.0318318318318318</v>
+        <v>0.0308030722147019</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>

--- a/synthetic_data/academic_validation_report.xlsx
+++ b/synthetic_data/academic_validation_report.xlsx
@@ -1423,10 +1423,10 @@
         <v>894</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.5123042505592841</v>
+        <v>0.5044742729306487</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1442,10 +1442,10 @@
         <v>912</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0.5120614035087719</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1461,10 +1461,10 @@
         <v>932</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.5064377682403434</v>
+        <v>0.4914163090128755</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -1543,28 +1543,28 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>6.809369562881911</v>
+        <v>6.831902738292663</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>2.575255655097496</v>
+        <v>2.590941389900695</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.05084745762711865</v>
+        <v>0.04601990049751244</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.1682808716707022</v>
+        <v>0.1716417910447761</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.1937046004842615</v>
+        <v>0.1965174129353234</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>0.1343825665859564</v>
+        <v>0.1368159203980099</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>0.2421307506053269</v>
+        <v>0.2475124378109453</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>0.2094430992736077</v>
+        <v>0.1965174129353234</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>6.644755088537025</v>
+        <v>6.682858470129588</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2.469338147191233</v>
+        <v>2.495151015185805</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.04522613065326633</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.07412060301507538</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.2964824120603015</v>
+        <v>0.2994791666666667</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.0414572864321608</v>
+        <v>0.03515625</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.2964824120603015</v>
+        <v>0.3138020833333333</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>0.2462311557788945</v>
+        <v>0.2239583333333333</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>6.964651602840553</v>
+        <v>6.949426835737116</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>2.682175589763646</v>
+        <v>2.673946834797088</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.05709624796084829</v>
+        <v>0.04568527918781726</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.2822185970636215</v>
+        <v>0.2910321489001692</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.07504078303425775</v>
+        <v>0.06937394247038917</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>0.2316476345840131</v>
+        <v>0.245346869712352</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.1435562805872757</v>
+        <v>0.1404399323181049</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>0.2104404567699837</v>
+        <v>0.2081218274111675</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
@@ -1746,10 +1746,10 @@
         <v>466</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.5128755364806867</v>
+        <v>0.5042918454935622</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1765,10 +1765,10 @@
         <v>464</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0.4719827586206897</v>
+        <v>0.4698275862068966</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1784,10 +1784,10 @@
         <v>469</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.4733475479744136</v>
+        <v>0.4584221748400853</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -1866,28 +1866,28 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>7.294876943096911</v>
+        <v>7.267342395587077</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>2.886249584205783</v>
+        <v>2.871325847123719</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.1415525114155251</v>
+        <v>0.1229314420803782</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.2237442922374429</v>
+        <v>0.2293144208037825</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.2511415525114155</v>
+        <v>0.2600472813238771</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>0.0958904109589041</v>
+        <v>0.09692671394799054</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>0.1689497716894977</v>
+        <v>0.1773049645390071</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>0.1187214611872146</v>
+        <v>0.1134751773049645</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1900,28 +1900,28 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>7.075305877994856</v>
+        <v>7.0474375</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2.750290344248728</v>
+        <v>2.7328125</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.1146341463414634</v>
+        <v>0.0975</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.08292682926829269</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.3780487804878049</v>
+        <v>0.395</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.05609756097560976</v>
+        <v>0.0575</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.2268292682926829</v>
+        <v>0.235</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>0.1341463414634146</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1934,28 +1934,28 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>7.544734575124126</v>
+        <v>7.486681084198384</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>3.044456690174251</v>
+        <v>3.009991349480969</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.1628664495114006</v>
+        <v>0.1384083044982699</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.3615635179153094</v>
+        <v>0.384083044982699</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.1433224755700326</v>
+        <v>0.1314878892733564</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>0.1433224755700326</v>
+        <v>0.1557093425605536</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.08794788273615635</v>
+        <v>0.08650519031141868</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>0.09771986970684039</v>
+        <v>0.1038062283737024</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
@@ -2107,10 +2107,10 @@
         <v>157</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.5031847133757962</v>
+        <v>0.464968152866242</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -2189,28 +2189,28 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>7.716682074223738</v>
+        <v>7.699739583333333</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>3.157480023271047</v>
+        <v>3.147493489583333</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2578125</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.2230769230769231</v>
+        <v>0.234375</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.2923076923076923</v>
+        <v>0.2890625</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>0.06153846153846154</v>
+        <v>0.0625</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>0.1</v>
+        <v>0.1015625</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.0546875</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2223,28 +2223,28 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>7.745482833825806</v>
+        <v>7.688169191919192</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3.183755100605037</v>
+        <v>3.15123106060606</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.2826086956521739</v>
+        <v>0.25</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.4855072463768116</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.05072463768115942</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.09848484848484848</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>0.007246376811594203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2257,28 +2257,28 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>7.815767314476835</v>
+        <v>7.752718855218855</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>3.208081915316705</v>
+        <v>3.177609427609428</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.2300884955752212</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.4070796460176991</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.1327433628318584</v>
+        <v>0.1313131313131313</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>0.1150442477876106</v>
+        <v>0.1313131313131313</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.07079646017699115</v>
+        <v>0.0707070707070707</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>0.04424778761061947</v>
+        <v>0.04040404040404041</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">

--- a/synthetic_data/academic_validation_report.xlsx
+++ b/synthetic_data/academic_validation_report.xlsx
@@ -979,7 +979,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="4140000"/>
+    <ext cx="7920000" cy="3888000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1006,7 +1006,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="4140000"/>
+    <ext cx="7920000" cy="3888000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1033,7 +1033,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="4140000"/>
+    <ext cx="7920000" cy="3888000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1372,7 +1372,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ĐẶC TRƯNG 1: TIẾN ĐỘ TỐT NGHIỆP VÀ PHÂN BỐ ĐIỂM SỐ SINH VIÊN (K20, K21, K22) | Quy mô: 6,703 SV (60.7% toàn trường)</t>
+          <t>BÁO CÁO HỌC VỤ: TIẾN ĐỘ TỐT NGHIỆP, XẾP LOẠI ĐIỂM &amp; TỶ LỆ BỎ HỌC (K20 - K26) | Quy mô: 6,703 SV (60.7% toàn trường)</t>
         </is>
       </c>
     </row>
@@ -1423,10 +1423,10 @@
         <v>894</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>451</v>
+        <v>506</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.5044742729306487</v>
+        <v>0.5659955257270693</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1442,10 +1442,10 @@
         <v>912</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5285087719298246</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1461,10 +1461,10 @@
         <v>932</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>458</v>
+        <v>514</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.4914163090128755</v>
+        <v>0.5515021459227468</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -1543,28 +1543,28 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>6.831902738292663</v>
+        <v>6.945755988792428</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>2.590941389900695</v>
+        <v>2.670855254832579</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.04601990049751244</v>
+        <v>0.049338146811071</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.1716417910447761</v>
+        <v>0.1660649819494585</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.1965174129353234</v>
+        <v>0.2093862815884477</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>0.1368159203980099</v>
+        <v>0.1335740072202166</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>0.2475124378109453</v>
+        <v>0.4416365824308063</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>0.1965174129353234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>6.682858470129588</v>
+        <v>6.87467448730367</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2.495151015185805</v>
+        <v>2.626924075896763</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.04724409448818898</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.08530183727034121</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.2994791666666667</v>
+        <v>0.3228346456692913</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.03515625</v>
+        <v>0.03805774278215223</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.3138020833333333</v>
+        <v>0.5065616797900262</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>0.2239583333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>6.949426835737116</v>
+        <v>7.150501072563236</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>2.673946834797088</v>
+        <v>2.807529907570962</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.04568527918781726</v>
+        <v>0.05255023183925812</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.2910321489001692</v>
+        <v>0.3137557959814529</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.06937394247038917</v>
+        <v>0.08964451313755796</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>0.245346869712352</v>
+        <v>0.2519319938176198</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.1404399323181049</v>
+        <v>0.2921174652241113</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>0.2081218274111675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
@@ -1642,8 +1642,183 @@
         </is>
       </c>
     </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>III. BẢNG 3: TỶ LỆ BỎ HỌC TỪNG KHÓA (KHÓA K20 ĐẾN K26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Khóa học</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Sĩ số tuyển sinh (SV)</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Sinh viên bỏ học (SV)</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Tỷ lệ bỏ học (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K20</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>894</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>0.07046979865771812</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Khóa K21</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>912</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0.01096491228070175</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K22</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>932</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>0.01072961373390558</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Khóa K23</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>986</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0.01115618661257606</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K24</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>0.015625</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Khóa K25</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>978</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0.01431492842535787</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K26</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>1041</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>0.01536983669548511</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>💡 Cách tính: Tỷ lệ bỏ học = Số sinh viên bỏ học (dropout = True) / Tổng sĩ số sinh viên của khóa.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A10:E10"/>
@@ -1651,6 +1826,7 @@
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1663,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1695,7 +1871,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ĐẶC TRƯNG 1: TIẾN ĐỘ TỐT NGHIỆP VÀ PHÂN BỐ ĐIỂM SỐ SINH VIÊN (K20, K21, K22) | Quy mô: 3,277 SV (29.7% toàn trường)</t>
+          <t>BÁO CÁO HỌC VỤ: TIẾN ĐỘ TỐT NGHIỆP, XẾP LOẠI ĐIỂM &amp; TỶ LỆ BỎ HỌC (K20 - K26) | Quy mô: 3,277 SV (29.7% toàn trường)</t>
         </is>
       </c>
     </row>
@@ -1746,10 +1922,10 @@
         <v>466</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.5042918454935622</v>
+        <v>0.8648068669527897</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1765,10 +1941,10 @@
         <v>464</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>218</v>
+        <v>403</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0.4698275862068966</v>
+        <v>0.8685344827586207</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1784,10 +1960,10 @@
         <v>469</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>215</v>
+        <v>401</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.4584221748400853</v>
+        <v>0.8550106609808102</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -1866,28 +2042,28 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>7.267342395587077</v>
+        <v>7.320655430711611</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>2.871325847123719</v>
+        <v>2.909794007490636</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.1229314420803782</v>
+        <v>0.1213483146067416</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.2293144208037825</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.2600472813238771</v>
+        <v>0.2651685393258427</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>0.09692671394799054</v>
+        <v>0.09662921348314607</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>0.1773049645390071</v>
+        <v>0.2921348314606741</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>0.1134751773049645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1900,28 +2076,28 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>7.0474375</v>
+        <v>7.166383181126332</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2.7328125</v>
+        <v>2.815848554033486</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.0975</v>
+        <v>0.1073059360730594</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0776255707762557</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.395</v>
+        <v>0.4200913242009132</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.0575</v>
+        <v>0.05707762557077625</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.235</v>
+        <v>0.3378995433789954</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1934,28 +2110,28 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>7.486681084198384</v>
+        <v>7.576694577352472</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>3.009991349480969</v>
+        <v>3.06966706539075</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.1384083044982699</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.384083044982699</v>
+        <v>0.3564593301435406</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.1314878892733564</v>
+        <v>0.1626794258373206</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>0.1557093425605536</v>
+        <v>0.1435406698564593</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.08650519031141868</v>
+        <v>0.1794258373205742</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>0.1038062283737024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
@@ -1965,8 +2141,183 @@
         </is>
       </c>
     </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>III. BẢNG 3: TỶ LỆ BỎ HỌC TỪNG KHÓA (KHÓA K20 ĐẾN K26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Khóa học</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Sĩ số tuyển sinh (SV)</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Sinh viên bỏ học (SV)</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Tỷ lệ bỏ học (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K20</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>466</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>0.04506437768240344</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Khóa K21</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>464</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K22</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>469</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Khóa K23</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>435</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K24</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>476</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Khóa K25</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>491</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K26</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>476</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>💡 Cách tính: Tỷ lệ bỏ học = Số sinh viên bỏ học (dropout = True) / Tổng sĩ số sinh viên của khóa.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A10:E10"/>
@@ -1974,6 +2325,7 @@
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1986,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2018,7 +2370,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ĐẶC TRƯNG 1: TIẾN ĐỘ TỐT NGHIỆP VÀ PHÂN BỐ ĐIỂM SỐ SINH VIÊN (K20, K21, K22) | Quy mô: 1,071 SV (9.7% toàn trường)</t>
+          <t>BÁO CÁO HỌC VỤ: TIẾN ĐỘ TỐT NGHIỆP, XẾP LOẠI ĐIỂM &amp; TỶ LỆ BỎ HỌC (K20 - K26) | Quy mô: 1,071 SV (9.7% toàn trường)</t>
         </is>
       </c>
     </row>
@@ -2069,10 +2421,10 @@
         <v>140</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.4714285714285714</v>
+        <v>0.9571428571428572</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2088,10 +2440,10 @@
         <v>153</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0.5359477124183006</v>
+        <v>0.9607843137254902</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -2107,10 +2459,10 @@
         <v>157</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.464968152866242</v>
+        <v>0.8662420382165605</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -2189,28 +2541,28 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>7.699739583333333</v>
+        <v>7.745328467153286</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>3.147493489583333</v>
+        <v>3.179470802919708</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.2578125</v>
+        <v>0.2554744525547445</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.234375</v>
+        <v>0.2408759124087591</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.2890625</v>
+        <v>0.2992700729927008</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>0.0625</v>
+        <v>0.06569343065693431</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>0.1015625</v>
+        <v>0.1386861313868613</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>0.0546875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2223,25 +2575,25 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>7.688169191919192</v>
+        <v>7.66858843537415</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3.15123106060606</v>
+        <v>3.139569160997732</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.06802721088435375</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.09848484848484848</v>
+        <v>0.08843537414965986</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0</v>
@@ -2257,28 +2609,28 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>7.752718855218855</v>
+        <v>7.826038647342995</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>3.177609427609428</v>
+        <v>3.223037439613526</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1884057971014493</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4565217391304348</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.1313131313131313</v>
+        <v>0.1594202898550725</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>0.1313131313131313</v>
+        <v>0.1014492753623188</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.09420289855072464</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>0.04040404040404041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
@@ -2288,8 +2640,183 @@
         </is>
       </c>
     </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>III. BẢNG 3: TỶ LỆ BỎ HỌC TỪNG KHÓA (KHÓA K20 ĐẾN K26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Khóa học</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Sĩ số tuyển sinh (SV)</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Sinh viên bỏ học (SV)</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Tỷ lệ bỏ học (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K20</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>0.02142857142857143</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Khóa K21</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>153</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K22</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Khóa K23</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K24</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>162</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Khóa K25</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Khóa K26</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>144</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>💡 Cách tính: Tỷ lệ bỏ học = Số sinh viên bỏ học (dropout = True) / Tổng sĩ số sinh viên của khóa.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A10:E10"/>
@@ -2297,6 +2824,7 @@
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/synthetic_data/academic_validation_report.xlsx
+++ b/synthetic_data/academic_validation_report.xlsx
@@ -1423,10 +1423,10 @@
         <v>894</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.5659955257270693</v>
+        <v>0.5559284116331096</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1442,10 +1442,10 @@
         <v>912</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0.5285087719298246</v>
+        <v>0.5274122807017544</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1461,10 +1461,10 @@
         <v>932</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.5515021459227468</v>
+        <v>0.5472103004291845</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -1543,25 +1543,25 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>6.945755988792428</v>
+        <v>6.943340416523752</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>2.670855254832579</v>
+        <v>2.669240240739153</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.049338146811071</v>
+        <v>0.04921968787515006</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.1660649819494585</v>
+        <v>0.1656662665066026</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.2093862815884477</v>
+        <v>0.2088835534213686</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>0.1335740072202166</v>
+        <v>0.1332533013205282</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>0.4416365824308063</v>
+        <v>0.4429771908763505</v>
       </c>
       <c r="J14" s="16" t="n">
         <v>0</v>
@@ -1577,25 +1577,25 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>6.87467448730367</v>
+        <v>6.874925269330246</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2.626924075896763</v>
+        <v>2.626986408339069</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.04724409448818898</v>
+        <v>0.04730617608409987</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.08530183727034121</v>
+        <v>0.08541392904073587</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.3228346456692913</v>
+        <v>0.3232588699080158</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.03805774278215223</v>
+        <v>0.03810775295663601</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.5065616797900262</v>
+        <v>0.5059132720105125</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0</v>
@@ -1611,25 +1611,25 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>7.150501072563236</v>
+        <v>7.155333900996993</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>2.807529907570962</v>
+        <v>2.810884912162329</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.05255023183925812</v>
+        <v>0.05279503105590062</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.3137557959814529</v>
+        <v>0.3152173913043478</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.08964451313755796</v>
+        <v>0.09006211180124224</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>0.2519319938176198</v>
+        <v>0.2531055900621118</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.2921174652241113</v>
+        <v>0.2888198757763975</v>
       </c>
       <c r="J16" s="16" t="n">
         <v>0</v>
@@ -1689,10 +1689,10 @@
         <v>894</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>0.07046979865771812</v>
+        <v>0.06823266219239374</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
@@ -1922,10 +1922,10 @@
         <v>466</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.8648068669527897</v>
+        <v>0.8540772532188842</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1941,10 +1941,10 @@
         <v>464</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0.8685344827586207</v>
+        <v>0.8642241379310345</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1960,10 +1960,10 @@
         <v>469</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.8550106609808102</v>
+        <v>0.8507462686567164</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>7.320655430711611</v>
+        <v>7.321142322097379</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>2.909794007490636</v>
+        <v>2.909971910112359</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>0.1213483146067416</v>
@@ -2076,25 +2076,25 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>7.166383181126332</v>
+        <v>7.17365634556575</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2.815848554033486</v>
+        <v>2.820422400611621</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.1073059360730594</v>
+        <v>0.1077981651376147</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.0776255707762557</v>
+        <v>0.07798165137614679</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.4200913242009132</v>
+        <v>0.4220183486238532</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.05707762557077625</v>
+        <v>0.05733944954128441</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.3378995433789954</v>
+        <v>0.3348623853211009</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0</v>
@@ -2110,25 +2110,25 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>7.576694577352472</v>
+        <v>7.587451807228915</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>3.06966706539075</v>
+        <v>3.07656626506024</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1590361445783132</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.3564593301435406</v>
+        <v>0.3590361445783132</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.1626794258373206</v>
+        <v>0.163855421686747</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>0.1435406698564593</v>
+        <v>0.144578313253012</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.1794258373205742</v>
+        <v>0.1734939759036145</v>
       </c>
       <c r="J16" s="16" t="n">
         <v>0</v>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>7.745328467153286</v>
+        <v>7.744701946472021</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>3.179470802919708</v>
+        <v>3.178923357664234</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>0.2554744525547445</v>
@@ -2609,25 +2609,25 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>7.826038647342995</v>
+        <v>7.839422141119219</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>3.223037439613526</v>
+        <v>3.231660583941605</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.1884057971014493</v>
+        <v>0.1897810218978102</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.4565217391304348</v>
+        <v>0.4598540145985401</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.1594202898550725</v>
+        <v>0.1605839416058394</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>0.1014492753623188</v>
+        <v>0.1021897810218978</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.09420289855072464</v>
+        <v>0.08759124087591241</v>
       </c>
       <c r="J16" s="16" t="n">
         <v>0</v>
